--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -59,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>ID</t>
   </si>
@@ -170,6 +175,24 @@
   </si>
   <si>
     <t>永恒天命</t>
+  </si>
+  <si>
+    <t>创世狂斩</t>
+  </si>
+  <si>
+    <t>创世破魂</t>
+  </si>
+  <si>
+    <t>创世血刃</t>
+  </si>
+  <si>
+    <t>创世屠龙</t>
+  </si>
+  <si>
+    <t>创世倚天</t>
+  </si>
+  <si>
+    <t>创世天命</t>
   </si>
   <si>
     <t>神圣怒斩</t>
@@ -1883,12 +1906,168 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="34" customFormat="1" ht="27" customHeight="1" spans="3:10">
+      <c r="C34">
+        <v>25</v>
+      </c>
+      <c r="D34" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34">
+        <v>5</v>
+      </c>
+      <c r="F34">
+        <v>1025</v>
+      </c>
+      <c r="G34" s="1">
+        <v>5</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>-1</v>
+      </c>
+      <c r="J34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" ht="27" customHeight="1" spans="3:10">
+      <c r="C35">
+        <v>26</v>
+      </c>
+      <c r="D35" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35">
+        <v>5</v>
+      </c>
+      <c r="F35">
+        <v>1026</v>
+      </c>
+      <c r="G35" s="1">
+        <v>5</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>-1</v>
+      </c>
+      <c r="J35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" ht="27" customHeight="1" spans="3:10">
+      <c r="C36">
+        <v>27</v>
+      </c>
+      <c r="D36" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36">
+        <v>5</v>
+      </c>
+      <c r="F36">
+        <v>1027</v>
+      </c>
+      <c r="G36" s="1">
+        <v>5</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>-1</v>
+      </c>
+      <c r="J36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" ht="27" customHeight="1" spans="3:10">
+      <c r="C37">
+        <v>28</v>
+      </c>
+      <c r="D37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37">
+        <v>5</v>
+      </c>
+      <c r="F37">
+        <v>1028</v>
+      </c>
+      <c r="G37" s="1">
+        <v>5</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>-1</v>
+      </c>
+      <c r="J37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" ht="27" customHeight="1" spans="3:10">
+      <c r="C38">
+        <v>29</v>
+      </c>
+      <c r="D38" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+      <c r="F38">
+        <v>1029</v>
+      </c>
+      <c r="G38" s="1">
+        <v>5</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>-1</v>
+      </c>
+      <c r="J38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" ht="27" customHeight="1" spans="3:10">
+      <c r="C39">
+        <v>30</v>
+      </c>
+      <c r="D39" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39">
+        <v>5</v>
+      </c>
+      <c r="F39">
+        <v>1030</v>
+      </c>
+      <c r="G39" s="1">
+        <v>5</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>-1</v>
+      </c>
+      <c r="J39">
+        <v>-1</v>
+      </c>
+    </row>
     <row r="48" spans="3:10">
       <c r="C48">
         <v>1000001</v>
       </c>
       <c r="D48" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E48" s="1">
         <v>0</v>
@@ -1914,7 +2093,7 @@
         <v>1000002</v>
       </c>
       <c r="D49" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
@@ -1940,7 +2119,7 @@
         <v>1000003</v>
       </c>
       <c r="D50" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
@@ -1966,7 +2145,7 @@
         <v>1000004</v>
       </c>
       <c r="D51" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E51" s="1">
         <v>0</v>
@@ -1992,7 +2171,7 @@
         <v>1000005</v>
       </c>
       <c r="D52" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E52" s="1">
         <v>0</v>
@@ -2018,7 +2197,7 @@
         <v>1000006</v>
       </c>
       <c r="D53" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
